--- a/artfynd/A 55850-2024 artfynd.xlsx
+++ b/artfynd/A 55850-2024 artfynd.xlsx
@@ -1158,7 +1158,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121744468</v>
+        <v>121745294</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1194,14 +1194,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slarven, Slarven, Jmt</t>
+          <t>Tvärån, Tvärån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446225</v>
+        <v>446352</v>
       </c>
       <c r="R6" t="n">
-        <v>7031919</v>
+        <v>7031636</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121745294</v>
+        <v>121744832</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1296,14 +1296,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tvärån, Tvärån, Jmt</t>
+          <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446352</v>
+        <v>446228</v>
       </c>
       <c r="R7" t="n">
-        <v>7031636</v>
+        <v>7031777</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121744832</v>
+        <v>121744468</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446228</v>
+        <v>446225</v>
       </c>
       <c r="R9" t="n">
-        <v>7031777</v>
+        <v>7031919</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 55850-2024 artfynd.xlsx
+++ b/artfynd/A 55850-2024 artfynd.xlsx
@@ -1158,7 +1158,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121745294</v>
+        <v>121744340</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1194,14 +1194,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tvärån, Tvärån, Jmt</t>
+          <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446352</v>
+        <v>446238</v>
       </c>
       <c r="R6" t="n">
-        <v>7031636</v>
+        <v>7031967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121744832</v>
+        <v>121744468</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446228</v>
+        <v>446225</v>
       </c>
       <c r="R7" t="n">
-        <v>7031777</v>
+        <v>7031919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121744340</v>
+        <v>121745199</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1398,14 +1398,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slarven, Slarven, Jmt</t>
+          <t>Tvärån, Tvärån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446238</v>
+        <v>446352</v>
       </c>
       <c r="R8" t="n">
-        <v>7031967</v>
+        <v>7031636</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121744468</v>
+        <v>121744832</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446225</v>
+        <v>446228</v>
       </c>
       <c r="R9" t="n">
-        <v>7031919</v>
+        <v>7031777</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 55850-2024 artfynd.xlsx
+++ b/artfynd/A 55850-2024 artfynd.xlsx
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121924483</v>
+        <v>121925469</v>
       </c>
       <c r="B11" t="n">
-        <v>77582</v>
+        <v>90779</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,13 +1708,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446196</v>
+        <v>446180</v>
       </c>
       <c r="R11" t="n">
-        <v>7031983</v>
+        <v>7031909</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121933715</v>
+        <v>121925917</v>
       </c>
       <c r="B12" t="n">
-        <v>79727</v>
+        <v>78808</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,30 +1797,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1828,16 +1828,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446324</v>
+        <v>446232</v>
       </c>
       <c r="R12" t="n">
-        <v>7031757</v>
+        <v>7031873</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1879,12 +1884,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På grenar på gammal gran under sälg (30 cm dbh) i gammal granskog</t>
+          <t>På gammal gran, 1,6 meters höjd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,19 +1904,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121926367</v>
+        <v>121924918</v>
       </c>
       <c r="B13" t="n">
         <v>78645</v>
@@ -1944,29 +1949,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446230</v>
+        <v>446183</v>
       </c>
       <c r="R13" t="n">
-        <v>7031833</v>
+        <v>7031941</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1993,24 +1989,9 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,19 +2006,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121924430</v>
+        <v>121925805</v>
       </c>
       <c r="B14" t="n">
         <v>78645</v>
@@ -2072,7 +2053,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2086,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446206</v>
+        <v>446220</v>
       </c>
       <c r="R14" t="n">
-        <v>7031993</v>
+        <v>7031858</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,12 +2112,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal granskog, längsta bål 40 cm lång</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,22 +2132,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121932258</v>
+        <v>121926166</v>
       </c>
       <c r="B15" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,43 +2160,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446246</v>
+        <v>446237</v>
       </c>
       <c r="R15" t="n">
-        <v>7031711</v>
+        <v>7031849</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,14 +2217,24 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>30cm långa</t>
+          <t>På bark på stam av levande gammal gran (35 cm dbh)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,22 +2249,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121925505</v>
+        <v>121931675</v>
       </c>
       <c r="B16" t="n">
-        <v>78729</v>
+        <v>90779</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,43 +2277,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446196</v>
+        <v>446219</v>
       </c>
       <c r="R16" t="n">
-        <v>7031885</v>
+        <v>7031652</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2336,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2346,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal klen gran i glänta i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog nära bäck</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121930998</v>
+        <v>121932210</v>
       </c>
       <c r="B17" t="n">
-        <v>58052</v>
+        <v>78901</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,43 +2394,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103044</v>
+        <v>6459</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446213</v>
+        <v>446234</v>
       </c>
       <c r="R17" t="n">
-        <v>7031646</v>
+        <v>7031703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,7 +2453,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2463,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på gren på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,22 +2483,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121929358</v>
+        <v>121929518</v>
       </c>
       <c r="B18" t="n">
-        <v>74747</v>
+        <v>74559</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2538,25 +2507,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,7 +2570,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,12 +2580,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark vid basen av gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,7 +2612,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121925805</v>
+        <v>121924430</v>
       </c>
       <c r="B19" t="n">
         <v>78645</v>
@@ -2678,7 +2647,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2692,10 +2661,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446220</v>
+        <v>446206</v>
       </c>
       <c r="R19" t="n">
-        <v>7031858</v>
+        <v>7031993</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2727,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2737,12 +2706,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, längsta bål 40 cm lång</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,22 +2726,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121932439</v>
+        <v>121926836</v>
       </c>
       <c r="B20" t="n">
-        <v>90797</v>
+        <v>77582</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2785,43 +2754,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slarven, Slarven, Jmt</t>
+          <t>Prostbölestigen, Alsen , Prostbölestigen, Alsen , Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446246</v>
+        <v>446239</v>
       </c>
       <c r="R20" t="n">
-        <v>7031711</v>
+        <v>7031797</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2851,14 +2811,24 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På 2 träd bredvid varandra</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,22 +2843,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121924933</v>
+        <v>121925104</v>
       </c>
       <c r="B21" t="n">
-        <v>90797</v>
+        <v>78645</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2901,36 +2871,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2939,13 +2904,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446177</v>
+        <v>446176</v>
       </c>
       <c r="R21" t="n">
-        <v>7031930</v>
+        <v>7031920</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2974,7 +2939,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2984,12 +2949,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På två gamla levande granar i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,22 +2969,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121926713</v>
+        <v>121932726</v>
       </c>
       <c r="B22" t="n">
-        <v>90744</v>
+        <v>74747</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3028,25 +2993,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3056,10 +3021,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446204</v>
+        <v>446258</v>
       </c>
       <c r="R22" t="n">
-        <v>7031883</v>
+        <v>7031757</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3089,9 +3054,24 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3106,22 +3086,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121925489</v>
+        <v>121926713</v>
       </c>
       <c r="B23" t="n">
-        <v>78645</v>
+        <v>90744</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3130,47 +3110,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446183</v>
+        <v>446204</v>
       </c>
       <c r="R23" t="n">
-        <v>7031941</v>
+        <v>7031883</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3203,11 +3174,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Längsta bål 40cm</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3234,7 +3200,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121924739</v>
+        <v>121934092</v>
       </c>
       <c r="B24" t="n">
         <v>74747</v>
@@ -3274,10 +3240,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446209</v>
+        <v>446301</v>
       </c>
       <c r="R24" t="n">
-        <v>7031972</v>
+        <v>7031738</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3309,7 +3275,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3319,12 +3285,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3339,22 +3305,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121932210</v>
+        <v>121932571</v>
       </c>
       <c r="B25" t="n">
-        <v>78901</v>
+        <v>74747</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3363,25 +3329,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3391,10 +3357,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446234</v>
+        <v>446224</v>
       </c>
       <c r="R25" t="n">
-        <v>7031703</v>
+        <v>7031726</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3426,7 +3392,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3436,12 +3402,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På bark på gren på gammal gran i gammal granskog</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3456,22 +3417,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121932378</v>
+        <v>121925628</v>
       </c>
       <c r="B26" t="n">
-        <v>78901</v>
+        <v>78729</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3480,38 +3441,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6459</v>
+        <v>283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446223</v>
+        <v>446205</v>
       </c>
       <c r="R26" t="n">
-        <v>7031718</v>
+        <v>7031898</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3543,7 +3513,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3553,12 +3523,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av död gråal i gammal granskog</t>
+          <t>På tunna kvistar på gammal klen gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3573,22 +3543,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121929230</v>
+        <v>121931898</v>
       </c>
       <c r="B27" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3601,43 +3571,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446151</v>
+        <v>446219</v>
       </c>
       <c r="R27" t="n">
-        <v>7031651</v>
+        <v>7031652</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3669,7 +3630,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,12 +3640,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gamla granar, längsta bål 40 cm</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3711,10 +3672,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121931675</v>
+        <v>121931683</v>
       </c>
       <c r="B28" t="n">
-        <v>90779</v>
+        <v>90744</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3723,25 +3684,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3751,13 +3712,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446219</v>
+        <v>446288</v>
       </c>
       <c r="R28" t="n">
-        <v>7031652</v>
+        <v>7031664</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3801,7 +3762,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog nära bäck</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3816,22 +3777,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121925469</v>
+        <v>121928803</v>
       </c>
       <c r="B29" t="n">
-        <v>90779</v>
+        <v>78808</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3840,41 +3801,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446180</v>
+        <v>446148</v>
       </c>
       <c r="R29" t="n">
-        <v>7031909</v>
+        <v>7031730</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3903,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3913,12 +3888,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gren på klen gammal gran (6 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3945,10 +3920,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121931898</v>
+        <v>121926454</v>
       </c>
       <c r="B30" t="n">
-        <v>74747</v>
+        <v>90779</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3961,34 +3936,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446219</v>
+        <v>446214</v>
       </c>
       <c r="R30" t="n">
-        <v>7031652</v>
+        <v>7031823</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4020,7 +4000,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4030,12 +4010,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4050,22 +4030,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121931930</v>
+        <v>121930998</v>
       </c>
       <c r="B31" t="n">
-        <v>78645</v>
+        <v>58052</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4074,38 +4054,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446219</v>
+        <v>446213</v>
       </c>
       <c r="R31" t="n">
-        <v>7031652</v>
+        <v>7031646</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4137,7 +4126,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4147,12 +4136,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4167,22 +4151,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121931611</v>
+        <v>121924739</v>
       </c>
       <c r="B32" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4195,21 +4179,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4219,10 +4203,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446213</v>
+        <v>446209</v>
       </c>
       <c r="R32" t="n">
-        <v>7031654</v>
+        <v>7031972</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4254,7 +4238,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4264,12 +4248,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog nära bäck</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4284,22 +4268,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121934092</v>
+        <v>121931930</v>
       </c>
       <c r="B33" t="n">
-        <v>74747</v>
+        <v>78645</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4312,21 +4296,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4336,10 +4320,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446301</v>
+        <v>446219</v>
       </c>
       <c r="R33" t="n">
-        <v>7031738</v>
+        <v>7031652</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4371,7 +4355,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4381,12 +4365,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4413,10 +4397,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121924712</v>
+        <v>121927894</v>
       </c>
       <c r="B34" t="n">
-        <v>77582</v>
+        <v>90744</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4425,25 +4409,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228579</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4453,10 +4437,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446197</v>
+        <v>446156</v>
       </c>
       <c r="R34" t="n">
-        <v>7031959</v>
+        <v>7031809</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4488,7 +4472,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4498,12 +4482,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På död gren på levande gammal grov gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4530,10 +4514,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121926836</v>
+        <v>121925505</v>
       </c>
       <c r="B35" t="n">
-        <v>77582</v>
+        <v>78729</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4546,34 +4530,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Prostbölestigen, Alsen , Prostbölestigen, Alsen , Jmt</t>
+          <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446239</v>
+        <v>446196</v>
       </c>
       <c r="R35" t="n">
-        <v>7031797</v>
+        <v>7031885</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4605,7 +4598,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4615,12 +4608,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal klen gran i glänta i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4647,10 +4640,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121933324</v>
+        <v>121924712</v>
       </c>
       <c r="B36" t="n">
-        <v>78729</v>
+        <v>77582</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4663,48 +4656,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446306</v>
+        <v>446197</v>
       </c>
       <c r="R36" t="n">
-        <v>7031780</v>
+        <v>7031959</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4736,7 +4715,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4746,12 +4725,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På tjock gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4766,22 +4745,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121925104</v>
+        <v>121927680</v>
       </c>
       <c r="B37" t="n">
-        <v>78645</v>
+        <v>74559</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4790,47 +4769,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446176</v>
+        <v>446154</v>
       </c>
       <c r="R37" t="n">
-        <v>7031920</v>
+        <v>7031813</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4862,7 +4832,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4872,12 +4842,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark vid basen av gammal grov gran (60 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4892,22 +4862,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121925628</v>
+        <v>121926823</v>
       </c>
       <c r="B38" t="n">
-        <v>78729</v>
+        <v>78645</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4920,26 +4890,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4953,10 +4923,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446205</v>
+        <v>446223</v>
       </c>
       <c r="R38" t="n">
-        <v>7031898</v>
+        <v>7031774</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4986,24 +4956,14 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal klen gran</t>
+          <t>30cm långa</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5018,22 +4978,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121927680</v>
+        <v>121928566</v>
       </c>
       <c r="B39" t="n">
-        <v>74559</v>
+        <v>77988</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5046,21 +5006,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6428</v>
+        <v>214</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörkhövdad spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Allocalicium adaequatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Nyl.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5070,10 +5030,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446154</v>
+        <v>446144</v>
       </c>
       <c r="R39" t="n">
-        <v>7031813</v>
+        <v>7031748</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5105,7 +5065,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5115,12 +5075,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal grov gran (60 cm dbh) i gammal granskog</t>
+          <t>På kvistar på gråal</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5135,22 +5095,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121924613</v>
+        <v>121924933</v>
       </c>
       <c r="B40" t="n">
-        <v>78645</v>
+        <v>90797</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5163,31 +5123,36 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5196,13 +5161,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446200</v>
+        <v>446177</v>
       </c>
       <c r="R40" t="n">
-        <v>7031954</v>
+        <v>7031930</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5231,7 +5196,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5241,12 +5206,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På två gamla levande granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5273,10 +5238,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121931683</v>
+        <v>121934069</v>
       </c>
       <c r="B41" t="n">
-        <v>90744</v>
+        <v>77582</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5285,25 +5250,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5313,13 +5278,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446288</v>
+        <v>446294</v>
       </c>
       <c r="R41" t="n">
-        <v>7031664</v>
+        <v>7031733</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5348,7 +5313,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5358,12 +5323,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5378,22 +5343,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121925917</v>
+        <v>121932378</v>
       </c>
       <c r="B42" t="n">
-        <v>78808</v>
+        <v>78901</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5402,52 +5367,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1249</v>
+        <v>6459</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446232</v>
+        <v>446223</v>
       </c>
       <c r="R42" t="n">
-        <v>7031873</v>
+        <v>7031718</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5479,7 +5430,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5489,12 +5440,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran, 1,6 meters höjd</t>
+          <t>På bark på stam av död gråal i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5509,22 +5460,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121928566</v>
+        <v>121926199</v>
       </c>
       <c r="B43" t="n">
-        <v>77988</v>
+        <v>77582</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5533,25 +5484,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>214</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörkhövdad spiklav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Allocalicium adaequatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) M.Prieto &amp; Wedin</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5561,13 +5512,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446144</v>
+        <v>446237</v>
       </c>
       <c r="R43" t="n">
-        <v>7031748</v>
+        <v>7031853</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5596,7 +5547,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5606,12 +5557,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På kvistar på gråal</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5626,22 +5577,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121927894</v>
+        <v>121924483</v>
       </c>
       <c r="B44" t="n">
-        <v>90744</v>
+        <v>77582</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5650,25 +5601,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5678,10 +5629,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446156</v>
+        <v>446196</v>
       </c>
       <c r="R44" t="n">
-        <v>7031809</v>
+        <v>7031983</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5713,7 +5664,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5723,12 +5674,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På död gren på levande gammal grov gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5755,10 +5706,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121929518</v>
+        <v>121927243</v>
       </c>
       <c r="B45" t="n">
-        <v>74559</v>
+        <v>78808</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5767,41 +5718,55 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6428</v>
+        <v>1249</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446151</v>
+        <v>446182</v>
       </c>
       <c r="R45" t="n">
-        <v>7031651</v>
+        <v>7031815</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5830,7 +5795,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5840,12 +5805,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran i gammal granskog</t>
+          <t>2 meter upp</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5860,22 +5825,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121928803</v>
+        <v>121927998</v>
       </c>
       <c r="B46" t="n">
-        <v>78808</v>
+        <v>90779</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5884,52 +5849,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>446148</v>
+        <v>446156</v>
       </c>
       <c r="R46" t="n">
-        <v>7031730</v>
+        <v>7031809</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5961,7 +5912,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5971,12 +5922,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gren på klen gammal gran (6 cm dbh) i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6003,10 +5954,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121926454</v>
+        <v>121933715</v>
       </c>
       <c r="B47" t="n">
-        <v>90779</v>
+        <v>79727</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6019,27 +5970,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6048,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>446214</v>
+        <v>446324</v>
       </c>
       <c r="R47" t="n">
-        <v>7031823</v>
+        <v>7031757</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6083,7 +6038,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6093,12 +6048,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På grenar på gammal gran under sälg (30 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6113,22 +6068,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121932691</v>
+        <v>121929358</v>
       </c>
       <c r="B48" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6141,43 +6096,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>446223</v>
+        <v>446151</v>
       </c>
       <c r="R48" t="n">
-        <v>7031718</v>
+        <v>7031651</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6209,7 +6155,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6219,12 +6165,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6251,10 +6197,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121927243</v>
+        <v>121924613</v>
       </c>
       <c r="B49" t="n">
-        <v>78808</v>
+        <v>78645</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6263,30 +6209,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6294,24 +6240,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446182</v>
+        <v>446200</v>
       </c>
       <c r="R49" t="n">
-        <v>7031815</v>
+        <v>7031954</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6340,7 +6281,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6350,12 +6291,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>2 meter upp</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6370,22 +6311,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121927898</v>
+        <v>121931611</v>
       </c>
       <c r="B50" t="n">
-        <v>78808</v>
+        <v>78645</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6394,55 +6335,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446152</v>
+        <v>446213</v>
       </c>
       <c r="R50" t="n">
-        <v>7031802</v>
+        <v>7031654</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6471,7 +6398,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6481,12 +6408,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gren på gammal gran som är 60cm i diameter</t>
+          <t>På gammal gran i gammal granskog nära bäck</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6501,22 +6428,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121934069</v>
+        <v>121932439</v>
       </c>
       <c r="B51" t="n">
-        <v>77582</v>
+        <v>90797</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6529,34 +6456,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>446294</v>
+        <v>446246</v>
       </c>
       <c r="R51" t="n">
-        <v>7031733</v>
+        <v>7031711</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6586,24 +6522,14 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På 2 träd bredvid varandra</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6618,22 +6544,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121932726</v>
+        <v>121926367</v>
       </c>
       <c r="B52" t="n">
-        <v>74747</v>
+        <v>78645</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6646,37 +6572,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>446258</v>
+        <v>446230</v>
       </c>
       <c r="R52" t="n">
-        <v>7031757</v>
+        <v>7031833</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6705,7 +6640,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6715,12 +6650,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6747,10 +6682,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121926823</v>
+        <v>121927898</v>
       </c>
       <c r="B53" t="n">
-        <v>78645</v>
+        <v>78808</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6759,30 +6694,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6790,19 +6725,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>446223</v>
+        <v>446152</v>
       </c>
       <c r="R53" t="n">
-        <v>7031774</v>
+        <v>7031802</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6829,14 +6769,24 @@
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-01-05</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>30cm långa</t>
+          <t>På gren på gammal gran som är 60cm i diameter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6851,22 +6801,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121932571</v>
+        <v>121933324</v>
       </c>
       <c r="B54" t="n">
-        <v>74747</v>
+        <v>78729</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6879,34 +6829,48 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446224</v>
+        <v>446306</v>
       </c>
       <c r="R54" t="n">
-        <v>7031726</v>
+        <v>7031780</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6938,7 +6902,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6948,7 +6912,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På tjock gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6975,10 +6944,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121926199</v>
+        <v>121929230</v>
       </c>
       <c r="B55" t="n">
-        <v>77582</v>
+        <v>78645</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6991,37 +6960,46 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446237</v>
+        <v>446151</v>
       </c>
       <c r="R55" t="n">
-        <v>7031853</v>
+        <v>7031651</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7050,7 +7028,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7060,12 +7038,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gamla granar, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7092,10 +7070,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121931133</v>
+        <v>121932691</v>
       </c>
       <c r="B56" t="n">
-        <v>77582</v>
+        <v>78645</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7108,34 +7086,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446160</v>
+        <v>446223</v>
       </c>
       <c r="R56" t="n">
-        <v>7031613</v>
+        <v>7031718</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7167,7 +7154,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7177,12 +7164,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7209,10 +7196,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121927998</v>
+        <v>121932258</v>
       </c>
       <c r="B57" t="n">
-        <v>90779</v>
+        <v>78645</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7225,34 +7212,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Slarven, Slarven, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>446156</v>
+        <v>446246</v>
       </c>
       <c r="R57" t="n">
-        <v>7031809</v>
+        <v>7031711</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7282,24 +7278,14 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>30cm långa</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7314,22 +7300,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121926166</v>
+        <v>121931133</v>
       </c>
       <c r="B58" t="n">
-        <v>74747</v>
+        <v>77582</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7342,21 +7328,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7366,10 +7352,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446237</v>
+        <v>446160</v>
       </c>
       <c r="R58" t="n">
-        <v>7031849</v>
+        <v>7031613</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7401,7 +7387,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7411,12 +7397,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (35 cm dbh)</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7443,10 +7429,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121927331</v>
+        <v>121968518</v>
       </c>
       <c r="B59" t="n">
-        <v>74559</v>
+        <v>79761</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7459,21 +7445,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6428</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7486,10 +7472,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446175</v>
+        <v>446321</v>
       </c>
       <c r="R59" t="n">
-        <v>7031823</v>
+        <v>7031757</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7521,7 +7507,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7531,12 +7517,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran i gammal granskog</t>
+          <t>riklig på gammal sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7548,6 +7534,21 @@
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7564,10 +7565,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121968518</v>
+        <v>121927424</v>
       </c>
       <c r="B60" t="n">
-        <v>79761</v>
+        <v>78729</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7576,25 +7577,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7607,10 +7608,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>446321</v>
+        <v>446162</v>
       </c>
       <c r="R60" t="n">
-        <v>7031757</v>
+        <v>7031821</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7642,7 +7643,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7652,12 +7653,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>riklig på gammal sälg</t>
+          <t>På tunna kvistar på gammal klen gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7669,21 +7670,6 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7700,10 +7686,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121927424</v>
+        <v>121927331</v>
       </c>
       <c r="B61" t="n">
-        <v>78729</v>
+        <v>74559</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7712,25 +7698,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>283</v>
+        <v>6428</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7743,10 +7729,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>446162</v>
+        <v>446175</v>
       </c>
       <c r="R61" t="n">
-        <v>7031821</v>
+        <v>7031823</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7778,7 +7764,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7788,12 +7774,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal klen gran i gammal granskog</t>
+          <t>På bark vid basen av gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
